--- a/templates/template-tiktok-inactive.xlsx
+++ b/templates/template-tiktok-inactive.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{361FA1E6-D8F6-4C19-B0A1-C4953BCBB588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E12110C-410F-43A5-84FF-D1AF60C669C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -692,12 +692,6 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -736,6 +730,12 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1269,73 +1269,73 @@
     <col min="8" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:9" hidden="1">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-    </row>
-    <row r="3" spans="1:9" s="3" customFormat="1">
-      <c r="A3" s="15" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1355,45 +1355,45 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="4" customFormat="1" ht="165.6">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="165.6">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1413,16 +1413,16 @@
       <c r="E6" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="13" t="s">
+      <c r="H6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1442,16 +1442,16 @@
       <c r="E7" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="13" t="s">
+      <c r="H7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1471,16 +1471,16 @@
       <c r="E8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="13" t="s">
+      <c r="H8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1500,16 +1500,16 @@
       <c r="E9" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="13" t="s">
+      <c r="H9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1529,16 +1529,16 @@
       <c r="E10" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="13" t="s">
+      <c r="H10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1558,16 +1558,16 @@
       <c r="E11" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="13" t="s">
+      <c r="H11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1587,16 +1587,16 @@
       <c r="E12" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="H12" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1616,16 +1616,16 @@
       <c r="E13" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="13" t="s">
+      <c r="H13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1645,16 +1645,16 @@
       <c r="E14" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="13" t="s">
+      <c r="H14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1674,16 +1674,16 @@
       <c r="E15" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="13" t="s">
+      <c r="H15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1703,16 +1703,16 @@
       <c r="E16" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="13" t="s">
+      <c r="H16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1732,16 +1732,16 @@
       <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="13" t="s">
+      <c r="H17" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1761,16 +1761,16 @@
       <c r="E18" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="13" t="s">
+      <c r="H18" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1790,16 +1790,16 @@
       <c r="E19" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="13" t="s">
+      <c r="H19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="11" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1819,16 +1819,16 @@
       <c r="E20" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="13" t="s">
+      <c r="H20" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1848,16 +1848,16 @@
       <c r="E21" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="13" t="s">
+      <c r="H21" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1877,16 +1877,16 @@
       <c r="E22" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22" s="13" t="s">
+      <c r="H22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1906,16 +1906,16 @@
       <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="13" t="s">
+      <c r="H23" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1935,16 +1935,16 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="13" t="s">
+      <c r="H24" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1964,16 +1964,16 @@
       <c r="E25" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" s="13" t="s">
+      <c r="H25" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1993,16 +1993,16 @@
       <c r="E26" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="13" t="s">
+      <c r="H26" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2022,16 +2022,16 @@
       <c r="E27" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H27" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I27" s="13" t="s">
+      <c r="H27" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2051,16 +2051,16 @@
       <c r="E28" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I28" s="13" t="s">
+      <c r="H28" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2080,16 +2080,16 @@
       <c r="E29" t="s">
         <v>123</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H29" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I29" s="13" t="s">
+      <c r="H29" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2109,16 +2109,16 @@
       <c r="E30" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H30" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="13" t="s">
+      <c r="H30" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2138,16 +2138,16 @@
       <c r="E31" t="s">
         <v>129</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H31" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I31" s="13" t="s">
+      <c r="H31" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2167,16 +2167,16 @@
       <c r="E32" t="s">
         <v>131</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H32" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="13" t="s">
+      <c r="H32" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2196,16 +2196,16 @@
       <c r="E33" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H33" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="13" t="s">
+      <c r="H33" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2225,16 +2225,16 @@
       <c r="E34" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I34" s="13" t="s">
+      <c r="H34" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2254,16 +2254,16 @@
       <c r="E35" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H35" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="13" t="s">
+      <c r="H35" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2283,16 +2283,16 @@
       <c r="E36" t="s">
         <v>129</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36" s="13" t="s">
+      <c r="H36" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
       <c r="E37" t="s">
         <v>131</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H37" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="13" t="s">
+      <c r="H37" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2341,16 +2341,16 @@
       <c r="E38" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H38" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I38" s="13" t="s">
+      <c r="H38" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2370,16 +2370,16 @@
       <c r="E39" t="s">
         <v>48</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H39" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I39" s="13" t="s">
+      <c r="H39" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I39" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2399,16 +2399,16 @@
       <c r="E40" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H40" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I40" s="13" t="s">
+      <c r="H40" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2428,16 +2428,16 @@
       <c r="E41" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I41" s="13" t="s">
+      <c r="H41" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I41" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
       <c r="E42" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H42" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I42" s="13" t="s">
+      <c r="H42" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I42" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2486,16 +2486,16 @@
       <c r="E43" t="s">
         <v>48</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H43" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="13" t="s">
+      <c r="H43" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I43" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2515,16 +2515,16 @@
       <c r="E44" t="s">
         <v>46</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H44" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I44" s="13" t="s">
+      <c r="H44" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2544,16 +2544,16 @@
       <c r="E45" t="s">
         <v>48</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H45" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I45" s="13" t="s">
+      <c r="H45" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2642,224 +2642,224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="7"/>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="54.75" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="73.5" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="135" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="37.5" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.8">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="16"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="16"/>
     </row>
     <row r="13" spans="1:3" ht="42.75" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="86.4">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="31.5" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="4"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="360">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C16" s="11"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" spans="1:3" ht="39" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" spans="1:3" ht="37.5" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="11"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" ht="90.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="11"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/templates/template-tiktok-inactive.xlsx
+++ b/templates/template-tiktok-inactive.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Music\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E12110C-410F-43A5-84FF-D1AF60C669C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A2291F0-56E9-47DE-8F76-770741E98707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
     <t>product_id</t>
   </si>
   <si>
-    <t>V3</t>
+    <t>V4</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -148,382 +148,382 @@
     <t>Cells in gray can be left blank.</t>
   </si>
   <si>
+    <t>Glasses (600036)</t>
+  </si>
+  <si>
+    <t>Gift Sets (963464)</t>
+  </si>
+  <si>
+    <t>Mugs (600042)</t>
+  </si>
+  <si>
+    <t>Cups &amp; Saucers (600095)</t>
+  </si>
+  <si>
+    <t>Candles (854152)</t>
+  </si>
+  <si>
+    <t>Cards &amp; Card Stock (855560)</t>
+  </si>
+  <si>
+    <t>Auction product</t>
+  </si>
+  <si>
+    <t>Tokopedia (1)</t>
+  </si>
+  <si>
+    <t>TikTok Shop and Tokopedia (0;1)</t>
+  </si>
+  <si>
+    <t>TikTok Shop (0)</t>
+  </si>
+  <si>
     <t>{"main_locale":""}</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>1731305244420048893</t>
+  </si>
+  <si>
+    <t>1731305244420114429</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>30600</t>
+  </si>
+  <si>
+    <t>DEFECT SALE A - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>1731305260076337149</t>
+  </si>
+  <si>
+    <t>1 Mug</t>
+  </si>
+  <si>
+    <t>129900</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran G Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305260076468221</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2 Mug</t>
+  </si>
+  <si>
+    <t>149900</t>
+  </si>
+  <si>
+    <t>1731305260076402685</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran B Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305280206571517</t>
+  </si>
+  <si>
+    <t>1731305280206702589</t>
+  </si>
+  <si>
+    <t>1731305280206637053</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1731305280002557949</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Kina Custom</t>
+  </si>
+  <si>
+    <t>1731305280002492413</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>1731305255697549309</t>
+  </si>
+  <si>
+    <t>23500</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Dara Tanapijak</t>
+  </si>
+  <si>
+    <t>1731305255697483773</t>
+  </si>
+  <si>
+    <t>1731305256116914173</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kina Orange Tanapijak</t>
+  </si>
+  <si>
+    <t>25500</t>
+  </si>
+  <si>
+    <t>1731305256116848637</t>
+  </si>
+  <si>
+    <t>DEFECT SALE C - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
+  </si>
+  <si>
+    <t>1731305280191563773</t>
+  </si>
+  <si>
+    <t>1731305280191629309</t>
+  </si>
+  <si>
+    <t>1731305244421425149</t>
+  </si>
+  <si>
+    <t>1731305244421490685</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran D Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305244421556221</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran I Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305260042979325</t>
+  </si>
+  <si>
+    <t>1731305260043044861</t>
+  </si>
+  <si>
+    <t>179900</t>
+  </si>
+  <si>
+    <t>1731305260043110397</t>
+  </si>
+  <si>
+    <t>Hitam</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>1731305243310393341</t>
+  </si>
+  <si>
+    <t>Cangkir Keramik 300ml - Simpo Series - Tanapijak - cangkir teh gelas</t>
+  </si>
+  <si>
+    <t>1731305243310327805</t>
+  </si>
+  <si>
+    <t>1731305243310458877</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>1731305243310524413</t>
+  </si>
+  <si>
+    <t>Cokelat</t>
+  </si>
+  <si>
+    <t>Biru Muda</t>
+  </si>
+  <si>
+    <t>1731305243310589949</t>
+  </si>
+  <si>
+    <t>1731305287094339581</t>
+  </si>
+  <si>
+    <t>DEFECT SALE B - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
+  </si>
+  <si>
+    <t>1731305287094405117</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran E Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305287002589181</t>
+  </si>
+  <si>
+    <t>1731305255133480957</t>
+  </si>
+  <si>
+    <t>1731305255133546493</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran H Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305243311638525</t>
+  </si>
+  <si>
     <t>1731305243311704061</t>
   </si>
   <si>
-    <t>Hampers Lebaran H Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1731305243311638525</t>
-  </si>
-  <si>
-    <t>Gift Sets (963464)</t>
-  </si>
-  <si>
-    <t>129900</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>1 Mug</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2 Mug</t>
-  </si>
-  <si>
-    <t>149900</t>
-  </si>
-  <si>
     <t>1731305243311769597</t>
   </si>
   <si>
-    <t>Cards &amp; Card Stock (855560)</t>
+    <t>1731305255133349885</t>
+  </si>
+  <si>
+    <t>1731305255133284349</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran A Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305255133415421</t>
+  </si>
+  <si>
+    <t>1731305255589545981</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran C Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305255589414909</t>
+  </si>
+  <si>
+    <t>1731305255589480445</t>
+  </si>
+  <si>
+    <t>1731305243309934589</t>
+  </si>
+  <si>
+    <t>13300</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Namu Series - Tanapijak - gelas kopi cangkir teh</t>
+  </si>
+  <si>
+    <t>1731305243310000125</t>
+  </si>
+  <si>
+    <t>1731305243310262269</t>
+  </si>
+  <si>
+    <t>1731305243310065661</t>
+  </si>
+  <si>
+    <t>1731305243310131197</t>
+  </si>
+  <si>
+    <t>Dark Orange</t>
+  </si>
+  <si>
+    <t>1731305243310196733</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1731305255587776509</t>
+  </si>
+  <si>
+    <t>[HAMPERS] Tungku Aroma Terapi Set - Oil Wax Burner | Tanapijak</t>
+  </si>
+  <si>
+    <t>1731305255587842045</t>
+  </si>
+  <si>
+    <t>128600</t>
+  </si>
+  <si>
+    <t>1731305244875917309</t>
+  </si>
+  <si>
+    <t>1731305244875851773</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran J Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>1731305244875982845</t>
+  </si>
+  <si>
+    <t>1731305280001574909</t>
+  </si>
+  <si>
+    <t>1731305280001509373</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Gelas Ocha Teh Kopi - Mug Ocha | Soja Tanapijak</t>
+  </si>
+  <si>
+    <t>23000</t>
+  </si>
+  <si>
+    <t>Ramadhan 1</t>
   </si>
   <si>
     <t>1731305244419459069</t>
   </si>
   <si>
-    <t>Ramadhan 1</t>
+    <t>3900</t>
   </si>
   <si>
     <t>Gift Card - Kartu Ucapan A6 - Kartu Hadiah | Tanapijak</t>
   </si>
   <si>
+    <t>1731305244419393533</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>1731305244419393533</t>
-  </si>
-  <si>
-    <t>3900</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1731305244419524605</t>
   </si>
   <si>
     <t>Ramadhan 2</t>
   </si>
   <si>
-    <t>1731305244419524605</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
     <t>1731305244419590141</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>1731305280191563773</t>
-  </si>
-  <si>
-    <t>Glasses (600036)</t>
-  </si>
-  <si>
-    <t>DEFECT SALE C - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
-  </si>
-  <si>
-    <t>1731305280191629309</t>
-  </si>
-  <si>
-    <t>30600</t>
-  </si>
-  <si>
-    <t>1731305244420048893</t>
-  </si>
-  <si>
-    <t>1731305244420114429</t>
-  </si>
-  <si>
-    <t>DEFECT SALE A - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
-  </si>
-  <si>
-    <t>1731305260042979325</t>
-  </si>
-  <si>
-    <t>1731305260043044861</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran I Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>179900</t>
-  </si>
-  <si>
-    <t>1731305260043110397</t>
-  </si>
-  <si>
-    <t>1731305255697549309</t>
-  </si>
-  <si>
-    <t>1731305255697483773</t>
-  </si>
-  <si>
-    <t>23500</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Dara Tanapijak</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran G Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305260076337149</t>
-  </si>
-  <si>
-    <t>1731305260076468221</t>
-  </si>
-  <si>
-    <t>1731305260076402685</t>
-  </si>
-  <si>
-    <t>[HAMPERS] Tungku Aroma Terapi Set - Oil Wax Burner | Tanapijak</t>
-  </si>
-  <si>
-    <t>1731305255587776509</t>
-  </si>
-  <si>
-    <t>Candles (854152)</t>
-  </si>
-  <si>
-    <t>128600</t>
-  </si>
-  <si>
-    <t>1731305255587842045</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1731305280002492413</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>Mugs (600042)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1731305280002557949</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Kina Custom</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran E Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305255133480957</t>
-  </si>
-  <si>
-    <t>1731305287002589181</t>
-  </si>
-  <si>
-    <t>1731305255133546493</t>
-  </si>
-  <si>
-    <t>1731305255589414909</t>
-  </si>
-  <si>
-    <t>1731305255589545981</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran C Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305255589480445</t>
-  </si>
-  <si>
-    <t>1731305287094339581</t>
-  </si>
-  <si>
-    <t>1731305287094405117</t>
-  </si>
-  <si>
-    <t>DEFECT SALE B - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
-  </si>
-  <si>
-    <t>1731305280001574909</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Gelas Ocha Teh Kopi - Mug Ocha | Soja Tanapijak</t>
-  </si>
-  <si>
-    <t>1731305280001509373</t>
-  </si>
-  <si>
-    <t>23000</t>
-  </si>
-  <si>
-    <t>1731305280206571517</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran B Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305280206702589</t>
-  </si>
-  <si>
-    <t>1731305280206637053</t>
-  </si>
-  <si>
-    <t>25500</t>
-  </si>
-  <si>
-    <t>1731305256116848637</t>
-  </si>
-  <si>
-    <t>1731305256116914173</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kina Orange Tanapijak</t>
-  </si>
-  <si>
-    <t>1731305243310000125</t>
-  </si>
-  <si>
-    <t>13300</t>
-  </si>
-  <si>
-    <t>Hitam</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Namu Series - Tanapijak - gelas kopi cangkir teh</t>
-  </si>
-  <si>
-    <t>1731305243309934589</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>1731305243310262269</t>
-  </si>
-  <si>
-    <t>1731305243310065661</t>
-  </si>
-  <si>
-    <t>Cokelat</t>
-  </si>
-  <si>
-    <t>1731305243310131197</t>
-  </si>
-  <si>
-    <t>Biru Muda</t>
-  </si>
-  <si>
-    <t>Dark Orange</t>
-  </si>
-  <si>
-    <t>1731305243310196733</t>
-  </si>
-  <si>
-    <t>1731305243310327805</t>
-  </si>
-  <si>
-    <t>Cups &amp; Saucers (600095)</t>
-  </si>
-  <si>
-    <t>Cangkir Keramik 300ml - Simpo Series - Tanapijak - cangkir teh gelas</t>
-  </si>
-  <si>
-    <t>19000</t>
-  </si>
-  <si>
-    <t>1731305243310393341</t>
-  </si>
-  <si>
-    <t>1731305243310458877</t>
-  </si>
-  <si>
-    <t>1731305243310524413</t>
-  </si>
-  <si>
-    <t>1731305243310589949</t>
-  </si>
-  <si>
     <t>1731305224183449597</t>
   </si>
   <si>
+    <t>1731305224183318525</t>
+  </si>
+  <si>
     <t>Hampers Lebaran F Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
   </si>
   <si>
-    <t>1731305224183318525</t>
-  </si>
-  <si>
     <t>1731305224183384061</t>
   </si>
   <si>
-    <t>1731305255133284349</t>
-  </si>
-  <si>
-    <t>1731305255133349885</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran A Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305255133415421</t>
-  </si>
-  <si>
-    <t>1731305244875851773</t>
-  </si>
-  <si>
-    <t>1731305244875917309</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran J Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305244875982845</t>
-  </si>
-  <si>
-    <t>1731305244421490685</t>
-  </si>
-  <si>
-    <t>1731305244421425149</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran D Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>1731305244421556221</t>
+    <t>Data usage statement</t>
   </si>
   <si>
     <t>By submitting the URLs, you hereby grant us a worldwide, irrevocable, royalty free, perpetual, non-exclusive license to use, reproduce, display, distribute, publicly perform, and communicate to the public, the URLs and any photographs, trademarks, logos displayed on the websites submitted ("Product Materials”). You confirm and represent that you either own all rights in and to the Product Materials or have obtained all necessary licenses to use them in this platform. You further release platform from any claims arising out of platform's use of the Product Materials.</t>
-  </si>
-  <si>
-    <t>Data usage statement</t>
-  </si>
-  <si>
-    <t>Auction product</t>
-  </si>
-  <si>
-    <t>TikTok Shop and Tokopedia (0;1)</t>
-  </si>
-  <si>
-    <t>TikTok Shop (0)</t>
-  </si>
-  <si>
-    <t>Tokopedia (1)</t>
   </si>
 </sst>
 </file>
@@ -692,6 +692,12 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -730,12 +736,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1270,31 +1270,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" hidden="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1305,41 +1305,41 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1">
-      <c r="A3" s="13" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="43.05" customHeight="1">
+      <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1355,452 +1355,452 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="165.6">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:9" s="4" customFormat="1" ht="150" customHeight="1">
+      <c r="A5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>41</v>
+      <c r="F9" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
         <v>97</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>95</v>
+      <c r="G19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1808,7 +1808,7 @@
         <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
         <v>98</v>
@@ -1817,19 +1817,19 @@
         <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>41</v>
+        <v>101</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1837,115 +1837,115 @@
         <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
         <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>41</v>
+        <v>103</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s">
         <v>104</v>
       </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>41</v>
+      <c r="F22" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1953,86 +1953,86 @@
         <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>41</v>
+      <c r="G25" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
         <v>113</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
       </c>
       <c r="D26" t="s">
         <v>115</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
         <v>113</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H27" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>41</v>
+      <c r="F27" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2040,115 +2040,115 @@
         <v>118</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G29" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H29" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>41</v>
+      <c r="F29" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
         <v>124</v>
       </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
       <c r="E31" t="s">
-        <v>129</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H31" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>41</v>
+      <c r="F31" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2156,28 +2156,28 @@
         <v>125</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>41</v>
+        <v>95</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2185,376 +2185,376 @@
         <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>41</v>
+        <v>101</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>41</v>
+        <v>103</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>41</v>
+      <c r="G35" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>129</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>41</v>
+        <v>132</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G39" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H39" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>41</v>
+      <c r="F39" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>41</v>
+      <c r="G40" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
       </c>
       <c r="C41" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" t="s">
         <v>148</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
+        <v>147</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="E41" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>41</v>
+      <c r="G41" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E42" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I42" s="11" t="s">
-        <v>41</v>
+        <v>155</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D43" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="G43" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="E43" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>41</v>
+      <c r="H43" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2642,224 +2642,224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="54.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="73.5" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="135" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="37.5" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.8">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="42.75" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="86.4">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="31.5" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" ht="360">
-      <c r="A16" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="9"/>
+      <c r="A16" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:3" ht="39" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:3" ht="37.5" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" spans="1:3" ht="90.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2878,7 +2878,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -2965,7 +2965,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -2984,17 +2984,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3064,7 +3064,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
